--- a/halo-growth-hvac/hvac-qualified-lead-tracker.xlsx
+++ b/halo-growth-hvac/hvac-qualified-lead-tracker.xlsx
@@ -148,7 +148,7 @@
     <t xml:space="preserve">Leads — one row per HVAC business submission</t>
   </si>
   <si>
-    <t xml:space="preserve">Populated automatically by Make.com once connected (see Make.com Setup tab), or paste in manually from a LinkedIn Campaign Manager CSV export meanwhile. Concept must be A or C exactly to match Campaign Summary's formulas.</t>
+    <t xml:space="preserve">Populated automatically by two Make.com scenarios (one per ad, see Make.com Setup tab), or paste in manually from a LinkedIn Campaign Manager CSV export meanwhile.</t>
   </si>
   <si>
     <t xml:space="preserve">Date</t>
@@ -211,31 +211,31 @@
     <t xml:space="preserve">Connecting LinkedIn Lead Gen Forms to this sheet via Make.com</t>
   </si>
   <si>
-    <t xml:space="preserve">I have no LinkedIn or Make.com access in this session, so this hasn't been built or tested. Steps below are the standard, documented way to do this in Make; verify against Make's actual current UI as you go.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. This file needs to be a Google Sheet, not a local .xlsx, for Make to write into it live. Upload/import this file into Google Sheets first (File &gt; Import &gt; Upload, replace spreadsheet, keeps the formulas and formatting).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. In Make.com, create a new Scenario. Add a trigger module: search for 'LinkedIn Lead Gen Ads', choose 'Watch Leads' (or the equivalent new-lead trigger). Connect your LinkedIn Ads account (needs admin access on the ad account running this campaign).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Select the specific Lead Gen Form built for this campaign ('HVAC 5-Opportunity Trial', per CLAUDE_BROWSER_LINKEDIN_BRIEF.md).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Add an action module: 'Google Sheets' -&gt; 'Add a Row'. Connect the Google account that owns the imported sheet from step 1, select this spreadsheet, and the 'Leads' tab.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. Map LinkedIn's form fields to this sheet's columns: Date -&gt; use Make's 'now' function, Company -&gt; Company, Contact name -&gt; Contact name, Email -&gt; Email, Phone -&gt; Phone. Concept (A/C), Qualified, and everything from 'Sales conversation held' onward are NOT in the LinkedIn form, leave those blank for manual entry after each lead comes in.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. Run the scenario once manually with a real or sample submission before scheduling it, confirm a row actually appears in the right columns.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7. Turn scheduling on (Make can run this near-instantly or on an interval). From this point, every new form submission should append a row automatically.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Which column is 'Concept (A/C)' matched to which ad? Make can't infer this from the form alone unless you build two separate scenarios (one per ad) or add a hidden form field per ad. Worth deciding before wiring this up, not after.</t>
+    <t xml:space="preserve">Decided: two separate Lead Gen Forms (one per ad), each with its own Make scenario, so Concept A/C attribution is automatic rather than guessed. I have no LinkedIn or Make.com access in this session, so this hasn't been built or tested; verify against Make's actual current UI as you go.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0. In Campaign Manager, build two Lead Gen Forms with identical content (same fields, headline, supporting copy, confirmation message from CLAUDE_BROWSER_LINKEDIN_BRIEF.md), one attached to Ad 1 (Concept A) and one to Ad 2 (Concept C). This replaces the earlier one-shared-form plan, needed so each Make scenario can watch its own form and know which concept it belongs to.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Import this file into Google Sheets first (File &gt; Import &gt; Upload, replace spreadsheet), Make writes to a live Google Sheet, not a local .xlsx.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Build Scenario 1 (Concept A): trigger module 'LinkedIn Lead Gen Ads' -&gt; 'Watch Leads', connect the LinkedIn Ads account, select the Concept A form specifically.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Action module: 'Google Sheets' -&gt; 'Add a Row', target this spreadsheet's 'Leads' tab. Map Date -&gt; now(), Company/Contact name/Email/Phone -&gt; the matching form fields, and set the 'Concept (A/C)' column to a static value: A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Build Scenario 2 (Concept C): identical to Scenario 1, but watching the Concept C form, and the 'Concept (A/C)' column set to a static value: C.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Qualified, Sales conversation held, Trial purchased, Repeat purchase, and Revenue are not in LinkedIn's form, leave those blank in both scenarios for manual entry after each lead comes in.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Run each scenario once manually with a test submission before scheduling, confirm the row lands in the right columns with the correct Concept value.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. Turn both scenarios on. From this point, every new form submission on either ad should append a correctly-attributed row automatically.</t>
   </si>
 </sst>
 </file>
@@ -394,7 +394,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -489,10 +489,6 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2697,7 +2693,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="30"/>
@@ -2773,13 +2769,13 @@
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
     </row>
-    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24" t="s">
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -2792,7 +2788,7 @@
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A11:D11"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
